--- a/data/trans_dic/P19D_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19D_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,52</t>
+          <t>2,71; 7,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,6</t>
+          <t>1,53; 5,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,85</t>
+          <t>2,71; 7,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,32</t>
+          <t>1,72; 5,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,75</t>
+          <t>1,48; 5,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 7,96</t>
+          <t>2,74; 8,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,75</t>
+          <t>2,65; 7,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,52</t>
+          <t>1,37; 3,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,8</t>
+          <t>2,51; 5,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,83</t>
+          <t>2,62; 5,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,55</t>
+          <t>3,06; 6,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,91</t>
+          <t>1,79; 3,91</t>
         </is>
       </c>
     </row>
@@ -804,47 +804,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>3,01%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,52%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,86</t>
+          <t>3,2; 9,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,49; 12,17</t>
+          <t>5,34; 11,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,06</t>
+          <t>4,26; 10,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,92</t>
+          <t>1,96; 5,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,31</t>
+          <t>1,79; 5,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 10,1</t>
+          <t>3,9; 10,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,68</t>
+          <t>2,99; 8,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,5</t>
+          <t>1,6; 4,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,63</t>
+          <t>2,91; 6,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 10,25</t>
+          <t>5,64; 10,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 8,3</t>
+          <t>4,43; 8,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,18</t>
+          <t>2,01; 4,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,07</t>
+          <t>5,23; 9,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,12; 16,07</t>
+          <t>9,74; 15,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 12,43</t>
+          <t>6,52; 12,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,79; 76,63</t>
+          <t>5,61; 11,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 11,16</t>
+          <t>3,03; 11,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 9,95</t>
+          <t>3,53; 9,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 16,26</t>
+          <t>5,86; 16,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,21</t>
+          <t>2,13; 7,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,23</t>
+          <t>5,05; 9,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,24; 13,13</t>
+          <t>8,49; 13,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 12,52</t>
+          <t>7,16; 12,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 69,94</t>
+          <t>5,12; 9,37</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 9,94</t>
+          <t>6,21; 9,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,74; 20,85</t>
+          <t>15,66; 21,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 10,41</t>
+          <t>6,56; 10,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 10,33</t>
+          <t>7,57; 11,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 9,04</t>
+          <t>4,67; 8,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,44; 12,21</t>
+          <t>7,38; 12,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,4</t>
+          <t>7,74; 12,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,7</t>
+          <t>3,23; 5,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 8,8</t>
+          <t>6,13; 8,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,79; 16,52</t>
+          <t>12,86; 16,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,55; 10,56</t>
+          <t>7,61; 10,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,15</t>
+          <t>6,01; 8,43</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 20,12</t>
+          <t>10,49; 19,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,66; 24,96</t>
+          <t>17,06; 24,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,51; 19,14</t>
+          <t>11,94; 18,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,21; 23,54</t>
+          <t>15,38; 23,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 10,01</t>
+          <t>4,97; 9,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,59</t>
+          <t>13,43; 19,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,55</t>
+          <t>7,47; 12,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 10,72</t>
+          <t>7,27; 10,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,76; 12,23</t>
+          <t>7,62; 12,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,83; 20,42</t>
+          <t>15,91; 20,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,12; 14,54</t>
+          <t>10,12; 14,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,59; 14,23</t>
+          <t>11,16; 14,79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,07</t>
+          <t>1,31; 6,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,03; 14,56</t>
+          <t>5,97; 13,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,91; 17,9</t>
+          <t>8,71; 17,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,35; 18,23</t>
+          <t>2,48; 13,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,0; 10,76</t>
+          <t>6,98; 10,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,82; 15,46</t>
+          <t>10,69; 15,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,16; 12,43</t>
+          <t>8,02; 12,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,41</t>
+          <t>6,16; 9,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,12; 9,3</t>
+          <t>6,23; 9,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,38; 14,21</t>
+          <t>10,21; 14,1</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,01; 12,62</t>
+          <t>8,97; 12,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,05; 10,22</t>
+          <t>5,96; 9,58</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,21; 8,33</t>
+          <t>6,18; 8,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,43; 14,95</t>
+          <t>12,33; 15,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,23; 10,48</t>
+          <t>8,09; 10,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,84; 34,57</t>
+          <t>7,45; 9,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,76</t>
+          <t>5,77; 7,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,8; 12,04</t>
+          <t>9,82; 12,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,75; 9,93</t>
+          <t>7,82; 9,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 5,99</t>
+          <t>5,05; 6,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,23; 7,67</t>
+          <t>6,33; 7,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,26; 13,08</t>
+          <t>11,33; 13,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,24; 9,78</t>
+          <t>8,29; 9,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,25; 21,82</t>
+          <t>6,43; 7,68</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24126</t>
+          <t>26929</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10877; 29146</t>
+          <t>10526; 28903</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6301; 22002</t>
+          <t>6007; 21854</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10212; 26495</t>
+          <t>10485; 27799</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8252; 26643</t>
+          <t>9368; 29995</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3990; 15419</t>
+          <t>3966; 15695</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7608; 23245</t>
+          <t>8005; 23905</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8495; 24489</t>
+          <t>8376; 24664</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5742; 15596</t>
+          <t>6617; 17095</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16585; 38022</t>
+          <t>16473; 39080</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17759; 39966</t>
+          <t>17973; 40130</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21644; 46018</t>
+          <t>21469; 44461</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16489; 36930</t>
+          <t>18433; 40108</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>11375</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23833</t>
+          <t>27043</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8867; 26586</t>
+          <t>9615; 28445</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21001; 46589</t>
+          <t>20437; 45611</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13514; 31735</t>
+          <t>13437; 32284</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8250; 22110</t>
+          <t>9393; 25005</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6764; 21050</t>
+          <t>5980; 19959</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12768; 31666</t>
+          <t>12241; 31479</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10493; 28969</t>
+          <t>9985; 27557</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5798; 17003</t>
+          <t>6683; 17982</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18195; 42009</t>
+          <t>18460; 41000</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38922; 71346</t>
+          <t>39286; 74245</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28255; 53911</t>
+          <t>28741; 53744</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16186; 34609</t>
+          <t>18039; 36857</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276717</t>
+          <t>37409</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>283148</t>
+          <t>44883</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21495; 43307</t>
+          <t>22516; 42645</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>54098; 85926</t>
+          <t>52068; 84712</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25687; 50379</t>
+          <t>26425; 49123</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44904; 507085</t>
+          <t>26057; 53332</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4162; 15628</t>
+          <t>4245; 16570</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7983; 23955</t>
+          <t>8510; 23941</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7992; 22674</t>
+          <t>8175; 22771</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3279; 11987</t>
+          <t>3958; 13222</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28404; 52670</t>
+          <t>28806; 52665</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63892; 101836</t>
+          <t>65854; 102283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39459; 68192</t>
+          <t>38996; 67461</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47482; 579003</t>
+          <t>33297; 61004</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83376</t>
+          <t>100360</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31566</t>
+          <t>36418</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>114942</t>
+          <t>136778</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>53691; 86714</t>
+          <t>54186; 85141</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>152671; 202170</t>
+          <t>151860; 204380</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58362; 91581</t>
+          <t>57690; 92353</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67499; 103250</t>
+          <t>82926; 123836</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27774; 53892</t>
+          <t>27869; 53206</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51802; 84983</t>
+          <t>51328; 86032</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52865; 84797</t>
+          <t>52946; 84281</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15815; 45083</t>
+          <t>27004; 46600</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89393; 129276</t>
+          <t>90028; 131505</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>213092; 275124</t>
+          <t>214227; 273712</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>118036; 165135</t>
+          <t>119049; 165143</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>78010; 139980</t>
+          <t>116037; 162797</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82109</t>
+          <t>95751</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>66771</t>
+          <t>71413</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>148880</t>
+          <t>167164</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26523; 49881</t>
+          <t>26016; 48337</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67018; 100414</t>
+          <t>68639; 100534</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48926; 81374</t>
+          <t>50779; 80277</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66503; 102924</t>
+          <t>78119; 117955</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23136; 45647</t>
+          <t>22668; 45584</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90639; 131618</t>
+          <t>90231; 128616</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41651; 69975</t>
+          <t>41617; 70606</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49184; 87517</t>
+          <t>57870; 85618</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>54664; 86134</t>
+          <t>53670; 86224</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>170073; 219316</t>
+          <t>170935; 221040</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99477; 142853</t>
+          <t>99484; 141948</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>120234; 178329</t>
+          <t>145635; 192930</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18440</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>56112</t>
+          <t>63042</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>74552</t>
+          <t>77462</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2772; 12879</t>
+          <t>2785; 12980</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13400; 32336</t>
+          <t>13271; 31011</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21532; 43230</t>
+          <t>21030; 43143</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7697; 41905</t>
+          <t>5527; 31065</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>66162; 101732</t>
+          <t>66013; 99997</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>100143; 143126</t>
+          <t>98937; 141265</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67280; 102394</t>
+          <t>66088; 100782</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>45070; 69799</t>
+          <t>50329; 78282</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>70883; 107637</t>
+          <t>72155; 108456</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>119135; 163058</t>
+          <t>117227; 161791</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>95995; 134443</t>
+          <t>95621; 136254</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>58821; 99376</t>
+          <t>61968; 99562</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>488438</t>
+          <t>279732</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>181043</t>
+          <t>200527</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>669482</t>
+          <t>480259</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>152131; 204155</t>
+          <t>151368; 201362</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>360974; 434152</t>
+          <t>358231; 437593</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>218403; 278139</t>
+          <t>214760; 277337</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>256903; 1133410</t>
+          <t>246910; 317785</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>159750; 212681</t>
+          <t>158155; 211946</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>307661; 377871</t>
+          <t>308417; 380215</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>221084; 283402</t>
+          <t>223229; 284359</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>145145; 210053</t>
+          <t>178439; 224201</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>323440; 398059</t>
+          <t>328514; 399414</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>680641; 790418</t>
+          <t>684986; 793960</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>453942; 538532</t>
+          <t>456456; 541856</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>423666; 1479939</t>
+          <t>440362; 526132</t>
         </is>
       </c>
     </row>
